--- a/August24_ExcelSheetReading_LoginRegister/HomeWorkTask1_ExcelSheetReading_KiranAcademy_RegisterPage.xlsx
+++ b/August24_ExcelSheetReading_LoginRegister/HomeWorkTask1_ExcelSheetReading_KiranAcademy_RegisterPage.xlsx
@@ -421,7 +421,7 @@
         <v>9876543210</v>
       </c>
       <c r="C2" t="str">
-        <v>kiran@gmail.com</v>
+        <v>patil@gmail.com</v>
       </c>
       <c r="D2" t="str">
         <v>123456</v>
